--- a/rules/CORE-000365/negative/02/data/unit-test-coreid-CG0077-negative 2.xlsx
+++ b/rules/CORE-000365/negative/02/data/unit-test-coreid-CG0077-negative 2.xlsx
@@ -470,7 +470,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sdtmig</v>
       </c>
       <c r="B2" s="4" t="str">
@@ -497,18 +497,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>mha.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>Medical History A</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="4" t="str">
         <v>mhb.xpt</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="4" t="str">
         <v>Medical History B</v>
       </c>
     </row>
@@ -521,7 +521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -548,7 +548,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <v>mha.xpt</v>
+        <v>mhb.xpt</v>
       </c>
       <c r="C2" s="2" t="str">
         <v>Record</v>
@@ -557,35 +557,35 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <v>CDISC001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <v>mhb.xpt</v>
+      </c>
+      <c r="C3" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D3" s="4">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4" t="str">
         <v>MHCAT</v>
       </c>
-      <c r="F2" s="2" t="str">
-        <v>GENERAL</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>mha.xpt</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D3" s="2">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="str">
-        <v>MHCAT</v>
-      </c>
-      <c r="F3" s="2" t="str">
+      <c r="F3" s="4" t="str">
         <v>GENERAL</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
         <v>mha.xpt</v>
@@ -594,21 +594,21 @@
         <v>Record</v>
       </c>
       <c r="D4" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="str">
-        <v>MHCAT</v>
+        <v>USUBJID</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>GENERAL</v>
+        <v>CDISC001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>mhb.xpt</v>
+        <v>mha.xpt</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>Record</v>
@@ -623,49 +623,9 @@
         <v>GENERAL</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <v>mhb.xpt</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D6" s="2">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v>MHCAT</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <v>GENERAL</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="str">
-        <v>mhb.xpt</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D7" s="2">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v>MHCAT</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <v>GENERAL</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -797,7 +757,7 @@
       <c r="B5" s="4" t="str">
         <v>MH</v>
       </c>
-      <c r="C5" s="4" t="str">
+      <c r="C5" s="7" t="str">
         <v>CDISC001</v>
       </c>
       <c r="D5" s="4">
@@ -823,7 +783,7 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="str">
+      <c r="E6" s="4" t="str">
         <v>GENERAL</v>
       </c>
       <c r="F6" s="4" t="str">
@@ -843,7 +803,7 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="4" t="str">
         <v>GENERAL</v>
       </c>
       <c r="F7" s="4" t="str">
@@ -984,7 +944,7 @@
       <c r="B5" s="4" t="str">
         <v>MH</v>
       </c>
-      <c r="C5" s="4" t="str">
+      <c r="C5" s="7" t="str">
         <v>CDISC001</v>
       </c>
       <c r="D5" s="4">
@@ -1010,7 +970,7 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="str">
+      <c r="E6" s="4" t="str">
         <v>GENERAL</v>
       </c>
       <c r="F6" s="4" t="str">
@@ -1030,7 +990,7 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="4" t="str">
         <v>GENERAL</v>
       </c>
       <c r="F7" s="4" t="str">

--- a/rules/CORE-000365/negative/02/data/unit-test-coreid-CG0077-negative 2.xlsx
+++ b/rules/CORE-000365/negative/02/data/unit-test-coreid-CG0077-negative 2.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -63,14 +63,9 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -78,12 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -119,7 +108,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -127,7 +116,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +509,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -544,31 +532,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>mhb.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="str">
-        <v>USUBJID</v>
-      </c>
-      <c r="F2" s="2" t="str">
-        <v>CDISC001</v>
+      <c r="E2" s="4" t="str">
+        <v>MHCAT</v>
+      </c>
+      <c r="F2" s="4" t="str">
+        <v>GENERAL</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4" t="str">
-        <v>mhb.xpt</v>
+        <v>mha.xpt</v>
       </c>
       <c r="C3" s="4" t="str">
         <v>Record</v>
@@ -583,49 +571,9 @@
         <v>GENERAL</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <v>mha.xpt</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D4" s="2">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v>USUBJID</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v>CDISC001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="str">
-        <v>mha.xpt</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v>MHCAT</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <v>GENERAL</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -667,86 +615,86 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Category for Medical History</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Reported Term for the Medical History</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Medical History Event Date Type</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Start Date/Time of Medical History Event</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Study Day of Start of Observation</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>50</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>19</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>13</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>8</v>
       </c>
     </row>
@@ -757,13 +705,13 @@
       <c r="B5" s="4" t="str">
         <v>MH</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="4" t="str">
         <v>CDISC001</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="6" t="str">
         <v>GENERAL</v>
       </c>
       <c r="F5" s="4" t="str">
@@ -851,89 +799,89 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Category for Medical History</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Reported Term for the Medical History</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Medical History Event Date Type</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Start Date/Time of Medical History Event</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Study Day of Start of Observation</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>50</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>19</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>13</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>8</v>
       </c>
     </row>
@@ -944,13 +892,13 @@
       <c r="B5" s="4" t="str">
         <v>MH</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="4" t="str">
         <v>CDISC001</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="6" t="str">
         <v>GENERAL</v>
       </c>
       <c r="F5" s="4" t="str">
